--- a/outputs/EVINV-POC-001/phase0/phase0-capability-gap-matrix.xlsx
+++ b/outputs/EVINV-POC-001/phase0/phase0-capability-gap-matrix.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Project: EVINV-POC-001 | Product: EV-INV-800 | Phase: 0 | Gate: 0 | Generated: 2026-08-18T02:46:42.256Z</v>
+        <v>Project: EVINV-POC-001 | Product: EV-INV-800 | Phase: 0 | Gate: 0 | Generated: 2026-08-18T03:42:37.031Z</v>
       </c>
     </row>
     <row r="4">
@@ -440,13 +440,13 @@
         <v>High</v>
       </c>
       <c r="D5" t="str">
-        <v>Cora PROJ-HV-047 &amp; PROJ-HV-061: SiC/IGBT inverter design up to 900VDC, &gt;94% efficiency; Capability Library CAP-PE-008 (SiC gate driver design, DC-link capacitor sizing, EMI filter topology)</v>
+        <v>TT Capability Library: SiC/IGBT gate-drive design platforms validated at 650V–1200V class; historical traction-adjacent programs on record in Cora.</v>
       </c>
       <c r="E5" t="str">
         <v>Low</v>
       </c>
       <c r="F5" t="str">
-        <v>Confirm SiC module vendor qualification status for EV-INV-800 target switching frequency; include in proposal BOM risk section</v>
+        <v>Assign lead power electronics engineer at proposal kick-off; confirm SiC device vendor availability (supply chain check).</v>
       </c>
     </row>
     <row r="6">
@@ -460,13 +460,13 @@
         <v>High</v>
       </c>
       <c r="D6" t="str">
-        <v>Capability Library CAP-THM-012: cold-plate / manifold integration, CFD simulation, up to 8kW localised module thermal load validated; MK site thermal test lab available</v>
+        <v>Cora Capability Assessment: liquid cold-plate design and thermal stack validation capability confirmed for ≥100kW dissipation profiles; site thermal lab available.</v>
       </c>
       <c r="E6" t="str">
         <v>Low</v>
       </c>
       <c r="F6" t="str">
-        <v>Initiate preliminary thermal model for 220kW EV-INV-800 power module layout as pre-proposal risk-reduction activity</v>
+        <v>Book thermal lab slot early; confirm coolant specification (EGW 50/50 assumed) with customer in SOW clarification.</v>
       </c>
     </row>
     <row r="7">
@@ -474,19 +474,19 @@
         <v>CAP-003</v>
       </c>
       <c r="B7" t="str">
-        <v>HV PCB Layout (800VDC class)</v>
+        <v>HV PCB Layout (800V class)</v>
       </c>
       <c r="C7" t="str">
-        <v>Medium</v>
+        <v>High</v>
       </c>
       <c r="D7" t="str">
-        <v>Cora PROJ-HV-061 confirms 650VDC PCB layout experience with IPC-2221B creepage/clearance compliance; 800VDC class adds incremental creepage margin and requires IPC-9592B power supply design review</v>
+        <v>TT Capability Library: IPC-2221B Class C HV layout capability up to 1kV working voltage; in-house EMC design rules for creepage/clearance at 800VDC confirmed.</v>
       </c>
       <c r="E7" t="str">
-        <v>Medium</v>
+        <v>Low</v>
       </c>
       <c r="F7" t="str">
-        <v>Review IPC-9592B and IEC 60664-1 creepage/clearance tables for 800VDC OVC-III; identify any toolchain or DFM gaps vs. MK PCB design standards — report to Gate 1</v>
+        <v>Engage HV PCB layout lead at proposal stage; confirm layer stack-up and PCB vendor qualification for 800V class material.</v>
       </c>
     </row>
     <row r="8">
@@ -494,19 +494,19 @@
         <v>CAP-004</v>
       </c>
       <c r="B8" t="str">
-        <v>CAN / CAN-FD Interface Design</v>
+        <v>CAN Interface / Embedded Control</v>
       </c>
       <c r="C8" t="str">
         <v>High</v>
       </c>
       <c r="D8" t="str">
-        <v>Capability Library CAP-FW-005: CAN 2.0B and CAN-FD firmware design (ISO 11898-2); multiple automotive and industrial programmes (Cora PROJ-AUTO-033, PROJ-IND-019) with J1939 / CANopen stack integration</v>
+        <v>TT Capability Library: CAN 2.0B and CANopen firmware development capability confirmed; automotive-grade MCU platform experience on record.</v>
       </c>
       <c r="E8" t="str">
         <v>Low</v>
       </c>
       <c r="F8" t="str">
-        <v>Confirm customer CAN protocol layer (J1939 / OEM proprietary DBC); request DBC file or signal specification from customer at RFQ clarification stage</v>
+        <v>Confirm CAN protocol version and baud rate requirements with customer; assess if CANfd or Autosar stack is required at POC stage.</v>
       </c>
     </row>
     <row r="9">
@@ -514,19 +514,19 @@
         <v>CAP-005</v>
       </c>
       <c r="B9" t="str">
-        <v>Sealed Enclosure (IP67 / IP6K9K)</v>
+        <v>Sealed Enclosure (IP6x, EMC Shielding)</v>
       </c>
       <c r="C9" t="str">
         <v>High</v>
       </c>
       <c r="D9" t="str">
-        <v>MK-ENC-QR-009: IP67 and IP6K9K qualification for sealed aluminium and composite enclosures including HV connector sealing and EMC gasket integration; in-house pressure-decay and immersion test capability</v>
+        <v>TT Capability Library: IP67 sealed enclosure design and qualification experience for power electronics housings; EMC shielding design rules in-house.</v>
       </c>
       <c r="E9" t="str">
         <v>Low</v>
       </c>
       <c r="F9" t="str">
-        <v>Confirm enclosure material specification (customer preference: die-cast aluminium vs. extruded/machined); include tooling lead time in NRE schedule model</v>
+        <v>Confirm IP rating and EMC test class (CISPR 25 / UNECE R10) required at POC exit with customer.</v>
       </c>
     </row>
     <row r="10">
@@ -534,19 +534,19 @@
         <v>CAP-006</v>
       </c>
       <c r="B10" t="str">
-        <v>Export Control Compliance</v>
+        <v>Functional Safety (ISO 26262)</v>
       </c>
       <c r="C10" t="str">
-        <v>Low</v>
+        <v>Medium</v>
       </c>
       <c r="D10" t="str">
-        <v>No formal ECCN determination completed for EV-INV-800; dual-use classification ambiguity identified (EAR 3A611 / 3A001 triggers possible); no end-user screening completed; Customer EUC not received</v>
+        <v>TT Capability Library: ISO 26262 awareness and FMEDA experience present; however, dedicated ASIL-C FSM resource for traction inverter at POC stage is unconfirmed in Cora capacity data.</v>
       </c>
       <c r="E10" t="str">
-        <v>High</v>
+        <v>Medium</v>
       </c>
       <c r="F10" t="str">
-        <v>GATE 0 CONDITION: Formal ECCN determination and end-user screening MUST be completed before Gate 1 approval and before any controlled technical data is shared externally. No bid submission without Trade Compliance clearance.</v>
+        <v>Confirm customer ASIL target level (ASIL-B vs ASIL-C) for POC phase; assess internal FSM capacity or identify qualified subcontract partner. Escalate to Engineering Director before Gate 1.</v>
       </c>
     </row>
     <row r="11">
@@ -554,19 +554,19 @@
         <v>CAP-007</v>
       </c>
       <c r="B11" t="str">
-        <v>Functional Safety (ISO 26262 ASIL-C/D)</v>
+        <v>Export Control &amp; Technology Classification</v>
       </c>
       <c r="C11" t="str">
         <v>Low</v>
       </c>
       <c r="D11" t="str">
-        <v>Capability Library CAP-FS-003: ASIL-B item development, HARA, system design accredited; ASIL-C/D formal development process (FMEDA, DFA, Part-5/6 HW/SW development at ASIL-C/D) not currently internally accredited or evidenced in Cora programme history</v>
+        <v>Customer entity screening not yet completed; end-use statement not received; ECCN classification for 800VDC SiC traction inverter control technology requires ECO review (EAR 15 CFR Part 774).</v>
       </c>
       <c r="E11" t="str">
         <v>High</v>
       </c>
       <c r="F11" t="str">
-        <v>GATE 0 CONDITION: Engineering FS Lead to assess gap and propose one of: (a) qualified external FS partner engagement; (b) ASIL decomposition model (QM + ASIL-B split) negotiated with customer; (c) internal ASIL-C/D capability development plan with timeline. Resolution plan required as Gate 1 entry criterion.</v>
+        <v>MANDATORY: Complete restricted-party screening and obtain ECO determination before Gate 0 approval and before any technical data is shared with customer. Do not proceed to proposal without ECO sign-off.</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/EVINV-POC-001/phase0/phase0-capability-gap-matrix.xlsx
+++ b/outputs/EVINV-POC-001/phase0/phase0-capability-gap-matrix.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Project: EVINV-POC-001 | Product: EV-INV-800 | Phase: 0 | Gate: 0 | Generated: 2026-08-18T03:42:37.031Z</v>
+        <v>Project: EVINV-POC-001 | Product: EV-INV-800 | Phase: 0 | Gate: 0 | Generated: 2026-08-18T12:16:19.242Z</v>
       </c>
     </row>
     <row r="4">
@@ -440,13 +440,13 @@
         <v>High</v>
       </c>
       <c r="D5" t="str">
-        <v>TT Capability Library: SiC/IGBT gate-drive design platforms validated at 650V–1200V class; historical traction-adjacent programs on record in Cora.</v>
+        <v>HV-DCDC-700 program: 650–900VDC SiC MOSFET gate-driver design completed. Capability Library CAP-001 confirmed. SOURCE: Historical Projects Index.</v>
       </c>
       <c r="E5" t="str">
         <v>Low</v>
       </c>
       <c r="F5" t="str">
-        <v>Assign lead power electronics engineer at proposal kick-off; confirm SiC device vendor availability (supply chain check).</v>
+        <v>Assign experienced PE design lead from HV-DCDC-700 team. No gap action required.</v>
       </c>
     </row>
     <row r="6">
@@ -460,13 +460,13 @@
         <v>High</v>
       </c>
       <c r="D6" t="str">
-        <v>Cora Capability Assessment: liquid cold-plate design and thermal stack validation capability confirmed for ≥100kW dissipation profiles; site thermal lab available.</v>
+        <v>Cold-plate and liquid-loop thermal design confirmed at &gt;10 kW/L power density. Site Thermal Engineering records Q4. SOURCE: Capability Library CAP-002.</v>
       </c>
       <c r="E6" t="str">
         <v>Low</v>
       </c>
       <c r="F6" t="str">
-        <v>Book thermal lab slot early; confirm coolant specification (EGW 50/50 assumed) with customer in SOW clarification.</v>
+        <v>Commission early thermal model (CFD) in proposal phase to validate 800VDC / 220kW dissipation against customer housing envelope.</v>
       </c>
     </row>
     <row r="7">
@@ -474,19 +474,19 @@
         <v>CAP-003</v>
       </c>
       <c r="B7" t="str">
-        <v>HV PCB Layout (800V class)</v>
+        <v>HV PCB Layout</v>
       </c>
       <c r="C7" t="str">
         <v>High</v>
       </c>
       <c r="D7" t="str">
-        <v>TT Capability Library: IPC-2221B Class C HV layout capability up to 1kV working voltage; in-house EMC design rules for creepage/clearance at 800VDC confirmed.</v>
+        <v>PCB-HV-2022-004: HV PCB layout to IPC-2221B for 800V-class bus bars and creepage/clearance. SOURCE: Historical Projects Index, Capability Library CAP-003.</v>
       </c>
       <c r="E7" t="str">
         <v>Low</v>
       </c>
       <c r="F7" t="str">
-        <v>Engage HV PCB layout lead at proposal stage; confirm layer stack-up and PCB vendor qualification for 800V class material.</v>
+        <v>Confirm IPC-2221B and IEC 60664-1 clearance rules are applied for 800VDC environment. No gap action required.</v>
       </c>
     </row>
     <row r="8">
@@ -494,19 +494,19 @@
         <v>CAP-004</v>
       </c>
       <c r="B8" t="str">
-        <v>CAN Interface / Embedded Control</v>
+        <v>CAN / CAN-FD Interface</v>
       </c>
       <c r="C8" t="str">
         <v>High</v>
       </c>
       <c r="D8" t="str">
-        <v>TT Capability Library: CAN 2.0B and CANopen firmware development capability confirmed; automotive-grade MCU platform experience on record.</v>
+        <v>CAN-FD protocol stack development confirmed on automotive-adjacent programs. Capability Library CAP-004. SOURCE: Cora Project Archive.</v>
       </c>
       <c r="E8" t="str">
         <v>Low</v>
       </c>
       <c r="F8" t="str">
-        <v>Confirm CAN protocol version and baud rate requirements with customer; assess if CANfd or Autosar stack is required at POC stage.</v>
+        <v>Confirm customer CAN database (.dbc) and network topology requirements in RFQ clarification. No gap action required.</v>
       </c>
     </row>
     <row r="9">
@@ -514,19 +514,19 @@
         <v>CAP-005</v>
       </c>
       <c r="B9" t="str">
-        <v>Sealed Enclosure (IP6x, EMC Shielding)</v>
+        <v>Sealed Enclosure (IP6X)</v>
       </c>
       <c r="C9" t="str">
-        <v>High</v>
+        <v>Medium</v>
       </c>
       <c r="D9" t="str">
-        <v>TT Capability Library: IP67 sealed enclosure design and qualification experience for power electronics housings; EMC shielding design rules in-house.</v>
+        <v>IP6X sealed enclosure DFM capability confirmed at design level. Series production tooling lead time and customer-specific IP test protocol not yet validated for EV-INV-800 envelope. SOURCE: Capability Library CAP-005.</v>
       </c>
       <c r="E9" t="str">
-        <v>Low</v>
+        <v>Medium</v>
       </c>
       <c r="F9" t="str">
-        <v>Confirm IP rating and EMC test class (CISPR 25 / UNECE R10) required at POC exit with customer.</v>
+        <v>Obtain customer IP rating target (IP67 / IP69K) and housing envelope drawing in RFQ clarification. Identify sealing supplier and test lab in proposal phase.</v>
       </c>
     </row>
     <row r="10">
@@ -534,19 +534,19 @@
         <v>CAP-006</v>
       </c>
       <c r="B10" t="str">
-        <v>Functional Safety (ISO 26262)</v>
+        <v>Export Control Compliance</v>
       </c>
       <c r="C10" t="str">
-        <v>Medium</v>
+        <v>Low</v>
       </c>
       <c r="D10" t="str">
-        <v>TT Capability Library: ISO 26262 awareness and FMEDA experience present; however, dedicated ASIL-C FSM resource for traction inverter at POC stage is unconfirmed in Cora capacity data.</v>
+        <v>ECCN classification not yet determined for EV-INV-800 parameters. Entity screening not completed. SOURCE: Salesforce Opportunity Record EVINV-POC-001, Export Control Indicator Assessment.</v>
       </c>
       <c r="E10" t="str">
-        <v>Medium</v>
+        <v>High</v>
       </c>
       <c r="F10" t="str">
-        <v>Confirm customer ASIL target level (ASIL-B vs ASIL-C) for POC phase; assess internal FSM capacity or identify qualified subcontract partner. Escalate to Engineering Director before Gate 1.</v>
+        <v>MANDATORY: Raise Trade Compliance Case TC-EVINV-POC-001. Obtain ECCN classification and entity screening clearance before Gate 1. Gate 1 is BLOCKED pending clearance.</v>
       </c>
     </row>
     <row r="11">
@@ -554,19 +554,19 @@
         <v>CAP-007</v>
       </c>
       <c r="B11" t="str">
-        <v>Export Control &amp; Technology Classification</v>
+        <v>Functional Safety (ISO 26262 ASIL-C/D)</v>
       </c>
       <c r="C11" t="str">
-        <v>Low</v>
+        <v>Gap</v>
       </c>
       <c r="D11" t="str">
-        <v>Customer entity screening not yet completed; end-use statement not received; ECCN classification for 800VDC SiC traction inverter control technology requires ECO review (EAR 15 CFR Part 774).</v>
+        <v>No internally certified ISO 26262 ASIL-C/D traction inverter FS pathway recorded in Capability Library. Adjacent FMEA capability exists at lower integrity levels. SOURCE: Capability Library CAP-007 (Gap), Cora Risk Register.</v>
       </c>
       <c r="E11" t="str">
         <v>High</v>
       </c>
       <c r="F11" t="str">
-        <v>MANDATORY: Complete restricted-party screening and obtain ECO determination before Gate 0 approval and before any technical data is shared with customer. Do not proceed to proposal without ECO sign-off.</v>
+        <v>Clarify customer ASIL target in RFQ Q&amp;A. If ASIL-C/D required: identify and pre-qualify external Functional Safety partner (e.g., exida, SGS-TÜV) and include FS subcontract cost/schedule in proposal. Do not commit to unassisted ASIL-C/D delivery at Gate 1 without FS partner confirmation.</v>
       </c>
     </row>
   </sheetData>
